--- a/education_enrollment_forms/030_cultural_center_language_admission_form--education_enrollment_forms.xlsx
+++ b/education_enrollment_forms/030_cultural_center_language_admission_form--education_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'language_course'}</t>
+          <t>language_course</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Language Course'}</t>
+          <t>Language Course</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'culture_course'}</t>
+          <t>culture_course</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Culture Course'}</t>
+          <t>Culture Course</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'art_course'}</t>
+          <t>art_course</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Art Course'}</t>
+          <t>Art Course</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'japanese'}</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Japanese'}</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'language_institute'}</t>
+          <t>language_institute</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Language Institute'}</t>
+          <t>Language Institute</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'culture_institute'}</t>
+          <t>culture_institute</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Culture Institute'}</t>
+          <t>Culture Institute</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'art_institute'}</t>
+          <t>art_institute</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Art Institute'}</t>
+          <t>Art Institute</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'proficient'}</t>
+          <t>proficient</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Proficient'}</t>
+          <t>Proficient</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'11-15'}</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '11-15'}</t>
+          <t>11-15</t>
         </is>
       </c>
     </row>
